--- a/Stats Sheet/Round Gaps/Scattershot.xlsx
+++ b/Stats Sheet/Round Gaps/Scattershot.xlsx
@@ -316,10 +316,10 @@
     <x:t>GoldenNs</x:t>
   </x:si>
   <x:si>
-    <x:t>gsjan</x:t>
-  </x:si>
-  <x:si>
     <x:t>HeroGolem5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>horayah</x:t>
   </x:si>
   <x:si>
     <x:t>Kaddyn</x:t>
